--- a/AAII_Financials/Quarterly/AIZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AIZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>AIZ</t>
   </si>
@@ -656,344 +656,351 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3454200</v>
+      </c>
+      <c r="E8" s="3">
         <v>3420100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3350400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3231500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3158400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3074000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3104800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2967700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2924900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2880100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2983100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2774100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2731600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2642800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2659500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2547800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2508100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2482200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2574900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2637800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2543500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2431600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2423800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2378000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2354500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2439500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2607900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2499500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2546100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2435900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2317100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2270800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1831700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1638600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1676600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1586800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1600600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1551900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1758500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1834200</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3000100</v>
+      </c>
+      <c r="E9" s="3">
         <v>3056200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2821300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2833800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2806000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2863500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2655300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2751800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2630900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2560400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2592600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2471500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2469100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2433500</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>8</v>
       </c>
@@ -1003,119 +1010,122 @@
       <c r="T9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V9" s="3">
         <v>932100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>965600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>991400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>946700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>901900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>927300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>867000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>895300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>859500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>869500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>815800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>777300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>740600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>750600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>463200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>346400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>346300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>332500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>346700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>314500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>344000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>330400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>454100</v>
+      </c>
+      <c r="E10" s="3">
         <v>363900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>529100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>397700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>352400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>210500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>449500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>215900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>294000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>319700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>390500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>302600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>262500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>209300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>8</v>
       </c>
@@ -1125,74 +1135,77 @@
       <c r="T10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V10" s="3">
         <v>1642800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1672200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1552100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1484900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1521900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1450700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1487500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1544200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1748400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1630000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1730300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1658600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1576500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1520200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1368500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1292200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1330300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1254300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1253900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1237400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1414500</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1503800</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,175 +1496,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>27300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>5400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>16000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>14500</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-500</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>20700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>139100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>7400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>5300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>31600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>40500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>500</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>400</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>100</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>400</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>29200</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E15" s="3">
         <v>66500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>156400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>62300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>59000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>56700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>139400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>58500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>50500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>50600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>109300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>45900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>47200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>48100</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3048900</v>
+      </c>
+      <c r="E17" s="3">
         <v>3056200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3011300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2871100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2842700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2863500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2822600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2789500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2665300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2560400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2713700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2505100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2501400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2462400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2535300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2513000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2411000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2280100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2389200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2422100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2275000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2218400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2232200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2240000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2123400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2328400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2371200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2370800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2336300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2192400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2247900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2168500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1727400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1480600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1506000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1682200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1409500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1324200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1689900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1599300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>405300</v>
+      </c>
+      <c r="E18" s="3">
         <v>363900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>339100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>360400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>315700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>210500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>282200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>178200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>259600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>319700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>269400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>269000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>230200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>180400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>124200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>34800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>97100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>202100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>185700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>215700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>268500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>213200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>191600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>138000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>231100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>111100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>236700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>128700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>209800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>243500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>69200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>102300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>104300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>158000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>170600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-95400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>191100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>227700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>68600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>234900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,8 +2130,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -2121,26 +2155,26 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>4900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>14500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-32500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-121100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
@@ -2174,101 +2208,104 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>472900</v>
+      </c>
+      <c r="E21" s="3">
         <v>430400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>495500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>422700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>374700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>267200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>421600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>236700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>310100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>370300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>378700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>314900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>277400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>228500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>166000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>79600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>145200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>249400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>231300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>257600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>311200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>254600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>224900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>178100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>267500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>159100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>242600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>34900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>240200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>273200</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2296,374 +2333,386 @@
       <c r="AP21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>28300</v>
+        <v>28400</v>
       </c>
       <c r="E22" s="3">
         <v>28300</v>
       </c>
       <c r="F22" s="3">
+        <v>28300</v>
+      </c>
+      <c r="G22" s="3">
         <v>27900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>26700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>26800</v>
       </c>
       <c r="I22" s="3">
         <v>26800</v>
       </c>
       <c r="J22" s="3">
-        <v>26700</v>
+        <v>26800</v>
       </c>
       <c r="K22" s="3">
         <v>26700</v>
       </c>
       <c r="L22" s="3">
-        <v>26800</v>
+        <v>26700</v>
       </c>
       <c r="M22" s="3">
         <v>26800</v>
       </c>
       <c r="N22" s="3">
+        <v>26800</v>
+      </c>
+      <c r="O22" s="3">
         <v>27000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>27200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>27000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>27900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>26300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>27200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>26900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>27100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>27500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>28800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>28400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>26800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>25500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>26700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>25500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>25400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>32200</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>26500</v>
       </c>
       <c r="AF22" s="3">
         <v>26500</v>
       </c>
       <c r="AG22" s="3">
+        <v>26500</v>
+      </c>
+      <c r="AH22" s="3">
         <v>26300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>26500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>21500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>12300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>12200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>12400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>12600</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>13900</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>14000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>376900</v>
+      </c>
+      <c r="E23" s="3">
         <v>335600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>283500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>331200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>289000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>183700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>250000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>151500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>232900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>292900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>226600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>228800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>204300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>147100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>96300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>69900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>175200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>158600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>188200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>239700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>184800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>158900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>112500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>209300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>100100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>178800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-24600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>183300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>217000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>42900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>75800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>78300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>136500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>158300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-107600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>178700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>215100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>54700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>220900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E24" s="3">
         <v>61500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>58300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>65600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>53700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>37100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>48700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>17700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>44200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>56500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>44100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>38700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>48000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>33500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>28200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>17700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>26200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>34600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>37200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>52600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>44000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>39800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>24500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>44600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-48500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>50000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>28600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>40700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>48400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>16300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>21300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>11300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>30500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>22400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-50300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>58500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>71300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>23400</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>76500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>298600</v>
+      </c>
+      <c r="E26" s="3">
         <v>274100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>225200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>265600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>235300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>146600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>201300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>133800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>188700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>236400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>182500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>190100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>156300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>113600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>68100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>52200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>149000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>124000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>151000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>187100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>140800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>119100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>88000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>164700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>148600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>128800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-53200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>142600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>168600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>26600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>54500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>67000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>106000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>135900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-57300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>120200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>143800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>31300</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>144400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>296300</v>
+      </c>
+      <c r="E27" s="3">
         <v>271800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>217500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>265600</v>
       </c>
-      <c r="G27" s="3">
-        <v>235300</v>
-      </c>
       <c r="H27" s="3">
+        <v>233200</v>
+      </c>
+      <c r="I27" s="3">
         <v>145200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>193600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>133800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>188700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>236400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>182500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>190100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>156300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>113600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>68100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>52200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>149000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>124000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>151000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>186900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>136300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>114600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>83600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>159800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>142800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>122900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-59500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>139500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>161000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>20300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>49800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>62200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>106000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>135900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-57300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>120200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>143800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>31300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>144400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3207,32 +3268,32 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-3100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>728800</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>18900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>14300</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>19900</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-118500</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>13700</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>7200</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3242,24 +3303,24 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>177000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,8 +3630,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3585,26 +3655,26 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>5900</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-14500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>32500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>121100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
@@ -3638,130 +3708,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>298600</v>
+      </c>
+      <c r="E33" s="3">
         <v>274100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>225200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>265600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>235300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>146600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>201300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>133800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>188700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>236400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>182500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>190100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>156300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>113600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>68100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>52200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>149000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>120900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>879800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>205800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>150600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>134500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-34900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>173500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>150000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>122900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-59500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>139500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>161000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>20300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>48300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>62200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>106000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>312900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-57300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>120200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>143800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>31300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>144400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>298600</v>
+      </c>
+      <c r="E35" s="3">
         <v>274100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>225200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>265600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>235300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>146600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>201300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>133800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>188700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>236400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>182500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>190100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>156300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>113600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>68100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>52200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>149000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>120900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>879800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>205800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>150600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>134500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-34900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>173500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>150000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>122900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-59500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>139500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>161000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>20300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>48300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>62200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>106000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>312900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-57300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>120200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>143800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>31300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>144400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,175 +4305,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1698700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1591700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1834100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1712500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1486700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1669600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1807700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1813400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1713100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1281900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1627400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1425300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1401700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1525600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1536700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1429800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1182000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1250900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2040800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2027900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2746000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1651300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2228600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2203000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2137500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1999900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1867100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1749300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1490400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1274200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1254000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1306600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1253700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2342000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>996800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>992800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>848200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>874500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1032000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1116600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>335200</v>
+      </c>
+      <c r="E42" s="3">
         <v>329800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>379500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>345800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>316300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>301300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>281600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>325000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>254000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>192800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>258100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>290400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>279700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>159100</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4463,130 +4553,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2008400</v>
+      </c>
+      <c r="E43" s="3">
         <v>2025300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1989400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1915600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1931300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1842700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2054000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1782600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1814800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2002700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2265600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2410200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2342300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2332200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2406400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2288900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2376900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2267500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1942500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1702400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1693600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1924200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1556400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1576700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1475400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1636000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1692800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1767100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1745700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1695500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1643500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1601000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1512700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1248500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1237300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1286400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1336300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1244000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1218000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1312700</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,53 +4803,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6483200</v>
+      </c>
+      <c r="E45" s="3">
         <v>6660700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7119100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7174900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7452400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7500500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7710000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7752100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6847800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6685700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6746200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6777300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6727300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6749400</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4829,53 +4928,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10525500</v>
+      </c>
+      <c r="E46" s="3">
         <v>10607500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11322100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11148800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11186700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11314100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11853300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11673100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10629700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10163100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10897300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10903200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10751000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10766300</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,374 +5053,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9816900</v>
+      </c>
+      <c r="E47" s="3">
         <v>9582600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9357800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9105500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8871800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8396000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7920400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8317200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7940700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7944800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7634100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7310300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7406200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7356200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7524500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7516100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7608000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8219100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8671600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9196600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7894000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7870000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>15679400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>15205900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>16317000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>15562000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>16587400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>16629000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>16516400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>16052100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>15125600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>15140400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>14748700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>12039500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>12426300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>11794000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>11677700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>11463800</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>11499500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>12033100</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>849600</v>
+      </c>
+      <c r="E48" s="3">
         <v>848900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>900900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>831100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>811500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>786300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>822400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>742200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>732600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>706100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>708800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>664400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>642700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>671200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>674700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>617600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>608800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>585300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>609100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>592600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>495200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>469100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>560300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>468400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>450100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>438100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>503200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>494600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>495900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>482800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>392500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>381700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>370600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>355200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>347600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>358400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>355500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>348800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>343600</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>337100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13524000</v>
+      </c>
+      <c r="E49" s="3">
         <v>13367000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13355900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13313400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13305200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13139900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13144400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13266600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13235300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13196800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13227000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13223600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13199600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13113200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3241900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3178400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3234400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3264500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3290800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3218300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3243100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3258700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3285500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2907600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3023500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2857200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2883600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2878800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2902100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2937700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2944200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2955300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3034000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1198900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1206300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1222600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1222000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1224500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1071300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1103000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,53 +5678,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1060000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1053000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1028200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1055100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1020900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1005800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>937600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1004200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>904500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>882100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>839300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>785300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>802500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>702800</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5615,23 +5735,23 @@
         <v>0</v>
       </c>
       <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>1050600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1076900</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
       <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
         <v>13648100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>13491500</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5647,8 +5767,8 @@
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
+      <c r="AE52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF52" s="3">
         <v>0</v>
@@ -5683,8 +5803,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36081400</v>
+      </c>
+      <c r="E54" s="3">
         <v>35768500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36289600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>35782100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>35525900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>34988400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>35020600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>35332300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33773000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>33225400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33635200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33208800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33104700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32915200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>33117300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>33245700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31728700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33022600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33920600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>33624800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>45994800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>44410600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>44649900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>43582600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>44233200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>43423300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>44291200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>43751500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>43139500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>42237000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>41089300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>43443100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>42361300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>32427900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>31843000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>32405200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>30058900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>29567700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>29709100</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>30283800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,130 +6145,134 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5837300</v>
+      </c>
+      <c r="E57" s="3">
         <v>5973800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5888700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5962900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6187500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6273900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6306900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6419400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5262500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5022900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5414000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5191400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5194900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5470600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2731500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2467200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2519500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2693300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3044400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2574400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2604900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2388300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2794900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2502100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2417300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2435900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2682100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2554900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2513800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2379900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2187400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2212100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2610700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1855800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2046300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2363000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2012300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1893400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1985700</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2009400</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6146,20 +6280,20 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>20300</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>174600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>174400</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -6176,13 +6310,13 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>50000</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -6259,175 +6393,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21105500</v>
+      </c>
+      <c r="E59" s="3">
         <v>20902700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21380900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20609200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20497200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20132500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>20211400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>20400000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20245300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>20031100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20110400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20119900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19931300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19671600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>23519300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>24143600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22219200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>21659800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>21743500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>21770000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>21107900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>20271300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>23585300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>23224500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>22265200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>21976900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>22425800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>22228800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>21650400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>21221400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>21012900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>22064900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>20845700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>12741400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>13348100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>14250700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>12237200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>12090200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>12213300</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>12242700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27566100</v>
+      </c>
+      <c r="E60" s="3">
         <v>27482500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27930500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27166300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27456600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>27166500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27077900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27345600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26019500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>25553000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26067200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>25913300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>25802900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>25752500</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,175 +6643,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2208100</v>
+      </c>
+      <c r="E61" s="3">
         <v>2207500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2260500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2206400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1909800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1909300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2145500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2082500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2081800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2081200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2115900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2080000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2079400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2078800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2129900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2129300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2128800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2203000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2202500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2201900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2550500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2203700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2252900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2008600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2208000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2207500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2006900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2006300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2007300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2006600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2006000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2005400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2004800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2004400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1068200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1067900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1136600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1067300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1067000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>1165600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>53800</v>
+      </c>
+      <c r="E62" s="3">
         <v>54700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>55700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>510100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>511700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>507100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>536700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>507900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>516700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>521500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>487200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>563300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>568700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>517600</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6679,23 +6825,23 @@
         <v>0</v>
       </c>
       <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
         <v>1037000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1064800</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
       <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
         <v>12484900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>12365200</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6711,8 +6857,8 @@
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
@@ -6747,8 +6893,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>29983500</v>
+      </c>
+      <c r="E66" s="3">
         <v>29899100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>30418000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>30023600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>30027400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29754200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29913900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30077000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>28768700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28305400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28825700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28718200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28618700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28518800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28888600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29146800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>27269000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28001500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28456500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>27880400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>40086400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>38588400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>38698500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>37646200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>38265400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>38053300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>38638400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>38092900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>37409300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>36796400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>35977300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>38223700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>37048800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>27938100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>27572400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>28267000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>25834300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>25408900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>25611000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>25778900</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7592,7 +7760,7 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="3">
         <v>2900</v>
@@ -7628,7 +7796,7 @@
         <v>2900</v>
       </c>
       <c r="AK70" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="AL70" s="3">
         <v>0</v>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5134300</v>
+      </c>
+      <c r="E72" s="3">
         <v>4949300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4826300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4726300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4570900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4431100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4378300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4321500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4309700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4194200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4028200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3990700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3877200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3775900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3699300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3678900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3774200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3976500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4041200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4219300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3640300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3635500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3548700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6126000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6194400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6061100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5966400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5882900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5980900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5879700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5759700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5777100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5846300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5815000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5697300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5414600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5500700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>5410800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>5296700</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>5295700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6097900</v>
+      </c>
+      <c r="E76" s="3">
         <v>5869400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5871600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5758500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5498500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5234200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5106700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5255300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5004300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4920000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4809500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4490600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4486000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4396400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4228700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4098900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4459700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5021100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5464100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5744400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5908400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5822200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5948500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5933500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5964900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5367100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5649900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5655700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5727300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5437700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5109100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5216500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5309600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4486900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4270600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4138200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4224600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4158800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4098100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>4504900</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>298600</v>
+      </c>
+      <c r="E81" s="3">
         <v>274100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>225200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>265600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>235300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>146600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>201300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>133800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>188700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>236400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>182500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>190100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>156300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>113600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>68100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>52200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>149000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>120900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>879800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>205800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>150600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>134500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-34900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>173500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>150000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>122900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-59500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>139500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>161000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>20300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>48300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>62200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>106000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>312900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-57300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>120200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>143800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>31300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>144400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,101 +8990,102 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E83" s="3">
         <v>38300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>41500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>33200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>33000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>12700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>27700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>28500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>29400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>41800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>27500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>31100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>29700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>41800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>44800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>48100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>47300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>45600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>41900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>42700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>41400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>39200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>40100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>31500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>33500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>38400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>27300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>30400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>29700</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH83" s="3" t="s">
         <v>8</v>
       </c>
@@ -8896,8 +9095,8 @@
       <c r="AJ83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK83" s="3">
-        <v>0</v>
+      <c r="AK83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL83" s="3">
         <v>0</v>
@@ -8914,8 +9113,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>454400</v>
+      </c>
+      <c r="E89" s="3">
         <v>240300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>671000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>505000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>265500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>392400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>102800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>436500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>710900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>82500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>362600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>330500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>185400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>259600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>277100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>647900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>173000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-501100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>254700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>947700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-418700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>440400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>609400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>415900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-123700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>245500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>442200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>479000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>246700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>202100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>304600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>225700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-75700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>164000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>366700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-24500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>24200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>177600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>258700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-45200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-47700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-59300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-62900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-59900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-53400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-68000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-47100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-55400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-50800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-54300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-50400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-49400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-48400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-52400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-46600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-46200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-41100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-56100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-46100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-45600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-39600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-40100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-24600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-21600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-39800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-25400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-23900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-20800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-21600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-18700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-12300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-16300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-14800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-103600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-224100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-282300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-403800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-269500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-362900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-421600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>71000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-207200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-193400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-328200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>3100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-157000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-254400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-229400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-127200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-241900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>120300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>120900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>3400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>18800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>14500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-460000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-243000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-214100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>181900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-162400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-447200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-298100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-389600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1593900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>79100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-299200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-245700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>62500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-58800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>94400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-114400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E96" s="3">
         <v>44000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>44200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>40600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>42700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>40900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>41100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>37500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>39900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>37400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>38500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>37100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>39700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>37000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-37500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-36700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-38600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-37400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-39100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-38500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-41800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-38200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-39500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-37500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-39600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-38000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-38300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-37300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-38300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-37400</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-37700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-35500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-30900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-29700</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-30200</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-28800</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-30300</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-29700</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-30300</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-30100</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-123300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-202600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-136200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-104300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-118700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-159700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-140800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-80800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-96200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-162000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-141500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-57400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-43000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-51200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-142300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-347400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-277500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-332400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-736600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>132200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-153000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>32000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-308800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-79400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>91400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-129100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-168700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-102300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>220900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>47600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>145900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>300500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1344000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>143000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>22600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-64600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-127700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-320000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-257300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E101" s="3">
         <v>9800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-19800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>11800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>8200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-15900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-22700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>8200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-15900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-22700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-16300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-8700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>13200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>7900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>15200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-16800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>7600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-4200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-20600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-3800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>4800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-10700</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-242400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>121600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>225800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-182900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-138100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>100300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>431200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-345500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>202100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>23600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-123900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>106900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>247800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-76800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-796000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>26900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-743900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1100200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-557000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>25600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>65500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>137600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>132800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>117800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>258900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>216200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>20200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-52600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>52900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1088300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1345200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>4000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>144600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-26300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-157500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-84600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-116100</v>
       </c>
     </row>
